--- a/BI/TP_BI/D004.xlsx
+++ b/BI/TP_BI/D004.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_95EB923B5E3DD1094B77DA45A450C0AE2B85DB8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -187,9 +201,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,7 +247,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,9 +266,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -292,9 +306,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -329,7 +343,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,7 +378,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,7 +551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -624,9 +638,9 @@
       <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="e">
+      <c r="L2" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42034.106461485746</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -663,9 +677,9 @@
       <c r="K3" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="2" t="e">
+      <c r="L3" s="2">
         <f t="shared" ref="L3:L66" ca="1" si="0">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40564.211767780696</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -702,9 +716,9 @@
       <c r="K4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="2" t="e">
+      <c r="L4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40711.465296221046</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -741,9 +755,9 @@
       <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="2" t="e">
+      <c r="L5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42104.958145727003</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -780,9 +794,9 @@
       <c r="K6" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="2" t="e">
+      <c r="L6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41928.53778300072</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -819,9 +833,9 @@
       <c r="K7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="2" t="e">
+      <c r="L7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41691.495208648252</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -858,9 +872,9 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="2" t="e">
+      <c r="L8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40945.891297428636</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -897,9 +911,9 @@
       <c r="K9" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="2" t="e">
+      <c r="L9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40577.761938132637</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -936,9 +950,9 @@
       <c r="K10" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="2" t="e">
+      <c r="L10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40504.309883853923</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -975,9 +989,9 @@
       <c r="K11" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="2" t="e">
+      <c r="L11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40885.139569958992</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1014,9 +1028,9 @@
       <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="2" t="e">
+      <c r="L12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41612.575067432481</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1053,9 +1067,9 @@
       <c r="K13" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="2" t="e">
+      <c r="L13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41492.993493152382</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1092,9 +1106,9 @@
       <c r="K14" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="2" t="e">
+      <c r="L14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41453.907096662428</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1131,9 +1145,9 @@
       <c r="K15" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="2" t="e">
+      <c r="L15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42350.43421802274</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1170,9 +1184,9 @@
       <c r="K16" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="2" t="e">
+      <c r="L16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40620.954191248209</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1209,9 +1223,9 @@
       <c r="K17" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="2" t="e">
+      <c r="L17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41917.7650950967</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1248,9 +1262,9 @@
       <c r="K18" t="s">
         <v>39</v>
       </c>
-      <c r="L18" s="2" t="e">
+      <c r="L18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41258.707660817461</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1287,9 +1301,9 @@
       <c r="K19" t="s">
         <v>39</v>
       </c>
-      <c r="L19" s="2" t="e">
+      <c r="L19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40630.283716130914</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1326,9 +1340,9 @@
       <c r="K20" t="s">
         <v>39</v>
       </c>
-      <c r="L20" s="2" t="e">
+      <c r="L20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40593.038884499016</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1365,9 +1379,9 @@
       <c r="K21" t="s">
         <v>22</v>
       </c>
-      <c r="L21" s="2" t="e">
+      <c r="L21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40912.672759091081</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1404,9 +1418,9 @@
       <c r="K22" t="s">
         <v>43</v>
       </c>
-      <c r="L22" s="2" t="e">
+      <c r="L22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42274.663512724765</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1443,9 +1457,9 @@
       <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="2" t="e">
+      <c r="L23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41709.42447388656</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1482,9 +1496,9 @@
       <c r="K24" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="2" t="e">
+      <c r="L24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41959.043406503821</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1521,9 +1535,9 @@
       <c r="K25" t="s">
         <v>18</v>
       </c>
-      <c r="L25" s="2" t="e">
+      <c r="L25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40453.801706246049</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1560,9 +1574,9 @@
       <c r="K26" t="s">
         <v>19</v>
       </c>
-      <c r="L26" s="2" t="e">
+      <c r="L26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41498.644637222402</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -1599,9 +1613,9 @@
       <c r="K27" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="2" t="e">
+      <c r="L27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41662.575483194618</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -1638,9 +1652,9 @@
       <c r="K28" t="s">
         <v>43</v>
       </c>
-      <c r="L28" s="2" t="e">
+      <c r="L28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40904.419237347473</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1677,9 +1691,9 @@
       <c r="K29" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="2" t="e">
+      <c r="L29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41848.3662518161</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -1716,9 +1730,9 @@
       <c r="K30" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="2" t="e">
+      <c r="L30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40340.171628099066</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1755,9 +1769,9 @@
       <c r="K31" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="2" t="e">
+      <c r="L31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41612.944071274644</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -1794,9 +1808,9 @@
       <c r="K32" t="s">
         <v>18</v>
       </c>
-      <c r="L32" s="2" t="e">
+      <c r="L32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40948.466075149947</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -1833,9 +1847,9 @@
       <c r="K33" t="s">
         <v>22</v>
       </c>
-      <c r="L33" s="2" t="e">
+      <c r="L33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41407.360198123213</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1872,9 +1886,9 @@
       <c r="K34" t="s">
         <v>31</v>
       </c>
-      <c r="L34" s="2" t="e">
+      <c r="L34" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40367.583474781975</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -1911,9 +1925,9 @@
       <c r="K35" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="2" t="e">
+      <c r="L35" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40202.611228103415</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -1950,9 +1964,9 @@
       <c r="K36" t="s">
         <v>16</v>
       </c>
-      <c r="L36" s="2" t="e">
+      <c r="L36" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40515.010187773732</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -1989,9 +2003,9 @@
       <c r="K37" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="2" t="e">
+      <c r="L37" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40535.959038423374</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2028,9 +2042,9 @@
       <c r="K38" t="s">
         <v>26</v>
       </c>
-      <c r="L38" s="2" t="e">
+      <c r="L38" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41153.132093863533</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2067,9 +2081,9 @@
       <c r="K39" t="s">
         <v>19</v>
       </c>
-      <c r="L39" s="2" t="e">
+      <c r="L39" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41399.839923567721</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2106,9 +2120,9 @@
       <c r="K40" t="s">
         <v>36</v>
       </c>
-      <c r="L40" s="2" t="e">
+      <c r="L40" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41449.952984004492</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2145,9 +2159,9 @@
       <c r="K41" t="s">
         <v>18</v>
       </c>
-      <c r="L41" s="2" t="e">
+      <c r="L41" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41654.889693799887</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2184,9 +2198,9 @@
       <c r="K42" t="s">
         <v>31</v>
       </c>
-      <c r="L42" s="2" t="e">
+      <c r="L42" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41581.734945258533</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2223,9 +2237,9 @@
       <c r="K43" t="s">
         <v>16</v>
       </c>
-      <c r="L43" s="2" t="e">
+      <c r="L43" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41411.174883019965</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2262,9 +2276,9 @@
       <c r="K44" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="2" t="e">
+      <c r="L44" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42060.660422369619</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2301,9 +2315,9 @@
       <c r="K45" t="s">
         <v>22</v>
       </c>
-      <c r="L45" s="2" t="e">
+      <c r="L45" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40563.777011325459</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2340,9 +2354,9 @@
       <c r="K46" t="s">
         <v>16</v>
       </c>
-      <c r="L46" s="2" t="e">
+      <c r="L46" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40574.901807861279</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2379,9 +2393,9 @@
       <c r="K47" t="s">
         <v>18</v>
       </c>
-      <c r="L47" s="2" t="e">
+      <c r="L47" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42234.75817807026</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2418,9 +2432,9 @@
       <c r="K48" t="s">
         <v>26</v>
       </c>
-      <c r="L48" s="2" t="e">
+      <c r="L48" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41376.415780364041</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2457,9 +2471,9 @@
       <c r="K49" t="s">
         <v>16</v>
       </c>
-      <c r="L49" s="2" t="e">
+      <c r="L49" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42089.541200998268</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2496,9 +2510,9 @@
       <c r="K50" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="2" t="e">
+      <c r="L50" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41142.25349254367</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2535,9 +2549,9 @@
       <c r="K51" t="s">
         <v>22</v>
       </c>
-      <c r="L51" s="2" t="e">
+      <c r="L51" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41979.836626817931</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -2574,9 +2588,9 @@
       <c r="K52" t="s">
         <v>36</v>
       </c>
-      <c r="L52" s="2" t="e">
+      <c r="L52" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42354.362953578333</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -2613,9 +2627,9 @@
       <c r="K53" t="s">
         <v>26</v>
       </c>
-      <c r="L53" s="2" t="e">
+      <c r="L53" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40814.51688243149</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -2652,9 +2666,9 @@
       <c r="K54" t="s">
         <v>19</v>
       </c>
-      <c r="L54" s="2" t="e">
+      <c r="L54" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41414.67202005921</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -2691,9 +2705,9 @@
       <c r="K55" t="s">
         <v>22</v>
       </c>
-      <c r="L55" s="2" t="e">
+      <c r="L55" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40808.820435570597</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -2730,9 +2744,9 @@
       <c r="K56" t="s">
         <v>19</v>
       </c>
-      <c r="L56" s="2" t="e">
+      <c r="L56" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42280.73314793691</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -2769,9 +2783,9 @@
       <c r="K57" t="s">
         <v>22</v>
       </c>
-      <c r="L57" s="2" t="e">
+      <c r="L57" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42122.293438249551</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -2808,9 +2822,9 @@
       <c r="K58" t="s">
         <v>14</v>
       </c>
-      <c r="L58" s="2" t="e">
+      <c r="L58" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40984.518001458644</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -2847,9 +2861,9 @@
       <c r="K59" t="s">
         <v>43</v>
       </c>
-      <c r="L59" s="2" t="e">
+      <c r="L59" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40701.588098619621</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -2886,9 +2900,9 @@
       <c r="K60" t="s">
         <v>22</v>
       </c>
-      <c r="L60" s="2" t="e">
+      <c r="L60" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41720.399601061952</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -2925,9 +2939,9 @@
       <c r="K61" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="2" t="e">
+      <c r="L61" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40397.389939273497</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -2964,9 +2978,9 @@
       <c r="K62" t="s">
         <v>43</v>
       </c>
-      <c r="L62" s="2" t="e">
+      <c r="L62" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40825.275282712842</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -3003,9 +3017,9 @@
       <c r="K63" t="s">
         <v>16</v>
       </c>
-      <c r="L63" s="2" t="e">
+      <c r="L63" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41402.254185210608</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -3042,9 +3056,9 @@
       <c r="K64" t="s">
         <v>31</v>
       </c>
-      <c r="L64" s="2" t="e">
+      <c r="L64" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41311.845723744649</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -3081,9 +3095,9 @@
       <c r="K65" t="s">
         <v>19</v>
       </c>
-      <c r="L65" s="2" t="e">
+      <c r="L65" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40891.712631893293</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -3120,9 +3134,9 @@
       <c r="K66" t="s">
         <v>39</v>
       </c>
-      <c r="L66" s="2" t="e">
+      <c r="L66" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42281.106082806808</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -3159,9 +3173,9 @@
       <c r="K67" t="s">
         <v>43</v>
       </c>
-      <c r="L67" s="2" t="e">
+      <c r="L67" s="2">
         <f t="shared" ref="L67:L130" ca="1" si="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42285.432660092549</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -3198,9 +3212,9 @@
       <c r="K68" t="s">
         <v>16</v>
       </c>
-      <c r="L68" s="2" t="e">
+      <c r="L68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41033.441524887145</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -3237,9 +3251,9 @@
       <c r="K69" t="s">
         <v>19</v>
       </c>
-      <c r="L69" s="2" t="e">
+      <c r="L69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41931.605434974605</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -3276,9 +3290,9 @@
       <c r="K70" t="s">
         <v>18</v>
       </c>
-      <c r="L70" s="2" t="e">
+      <c r="L70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40583.635611942358</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -3315,9 +3329,9 @@
       <c r="K71" t="s">
         <v>18</v>
       </c>
-      <c r="L71" s="2" t="e">
+      <c r="L71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40859.08854444894</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -3354,9 +3368,9 @@
       <c r="K72" t="s">
         <v>26</v>
       </c>
-      <c r="L72" s="2" t="e">
+      <c r="L72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40661.696077588123</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -3393,9 +3407,9 @@
       <c r="K73" t="s">
         <v>31</v>
       </c>
-      <c r="L73" s="2" t="e">
+      <c r="L73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40259.411718868738</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -3432,9 +3446,9 @@
       <c r="K74" t="s">
         <v>36</v>
       </c>
-      <c r="L74" s="2" t="e">
+      <c r="L74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42169.844955404835</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -3471,9 +3485,9 @@
       <c r="K75" t="s">
         <v>36</v>
       </c>
-      <c r="L75" s="2" t="e">
+      <c r="L75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41291.433212609685</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -3510,9 +3524,9 @@
       <c r="K76" t="s">
         <v>14</v>
       </c>
-      <c r="L76" s="2" t="e">
+      <c r="L76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42190.31847237749</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -3549,9 +3563,9 @@
       <c r="K77" t="s">
         <v>19</v>
       </c>
-      <c r="L77" s="2" t="e">
+      <c r="L77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41959.834008327125</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -3588,9 +3602,9 @@
       <c r="K78" t="s">
         <v>16</v>
       </c>
-      <c r="L78" s="2" t="e">
+      <c r="L78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40325.551657257914</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -3627,9 +3641,9 @@
       <c r="K79" t="s">
         <v>43</v>
       </c>
-      <c r="L79" s="2" t="e">
+      <c r="L79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41080.675441984007</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -3666,9 +3680,9 @@
       <c r="K80" t="s">
         <v>14</v>
       </c>
-      <c r="L80" s="2" t="e">
+      <c r="L80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41147.272043875608</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -3705,9 +3719,9 @@
       <c r="K81" t="s">
         <v>39</v>
       </c>
-      <c r="L81" s="2" t="e">
+      <c r="L81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42267.518255955518</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -3744,9 +3758,9 @@
       <c r="K82" t="s">
         <v>18</v>
       </c>
-      <c r="L82" s="2" t="e">
+      <c r="L82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40895.777346809387</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -3783,9 +3797,9 @@
       <c r="K83" t="s">
         <v>39</v>
       </c>
-      <c r="L83" s="2" t="e">
+      <c r="L83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41642.525568467492</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -3822,9 +3836,9 @@
       <c r="K84" t="s">
         <v>39</v>
       </c>
-      <c r="L84" s="2" t="e">
+      <c r="L84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42207.022028553911</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -3861,9 +3875,9 @@
       <c r="K85" t="s">
         <v>39</v>
       </c>
-      <c r="L85" s="2" t="e">
+      <c r="L85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42201.672250867181</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -3900,9 +3914,9 @@
       <c r="K86" t="s">
         <v>43</v>
       </c>
-      <c r="L86" s="2" t="e">
+      <c r="L86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41249.576217316928</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -3939,9 +3953,9 @@
       <c r="K87" t="s">
         <v>14</v>
       </c>
-      <c r="L87" s="2" t="e">
+      <c r="L87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42082.644340015395</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -3978,9 +3992,9 @@
       <c r="K88" t="s">
         <v>43</v>
       </c>
-      <c r="L88" s="2" t="e">
+      <c r="L88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41009.082444080108</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
@@ -4017,9 +4031,9 @@
       <c r="K89" t="s">
         <v>22</v>
       </c>
-      <c r="L89" s="2" t="e">
+      <c r="L89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41371.311186793129</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -4056,9 +4070,9 @@
       <c r="K90" t="s">
         <v>39</v>
       </c>
-      <c r="L90" s="2" t="e">
+      <c r="L90" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40513.562205568109</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -4095,9 +4109,9 @@
       <c r="K91" t="s">
         <v>22</v>
       </c>
-      <c r="L91" s="2" t="e">
+      <c r="L91" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41253.77707627145</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -4134,9 +4148,9 @@
       <c r="K92" t="s">
         <v>39</v>
       </c>
-      <c r="L92" s="2" t="e">
+      <c r="L92" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41287.21612244047</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -4173,9 +4187,9 @@
       <c r="K93" t="s">
         <v>39</v>
       </c>
-      <c r="L93" s="2" t="e">
+      <c r="L93" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41007.873811702739</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
@@ -4212,9 +4226,9 @@
       <c r="K94" t="s">
         <v>26</v>
       </c>
-      <c r="L94" s="2" t="e">
+      <c r="L94" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40774.363109967853</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -4251,9 +4265,9 @@
       <c r="K95" t="s">
         <v>22</v>
       </c>
-      <c r="L95" s="2" t="e">
+      <c r="L95" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40467.353820433746</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -4290,9 +4304,9 @@
       <c r="K96" t="s">
         <v>26</v>
       </c>
-      <c r="L96" s="2" t="e">
+      <c r="L96" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40922.541851998176</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -4329,9 +4343,9 @@
       <c r="K97" t="s">
         <v>19</v>
       </c>
-      <c r="L97" s="2" t="e">
+      <c r="L97" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41287.714682152495</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -4368,9 +4382,9 @@
       <c r="K98" t="s">
         <v>43</v>
       </c>
-      <c r="L98" s="2" t="e">
+      <c r="L98" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41933.398092643525</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -4407,9 +4421,9 @@
       <c r="K99" t="s">
         <v>16</v>
       </c>
-      <c r="L99" s="2" t="e">
+      <c r="L99" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41277.417755614573</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -4446,9 +4460,9 @@
       <c r="K100" t="s">
         <v>14</v>
       </c>
-      <c r="L100" s="2" t="e">
+      <c r="L100" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40437.3578028294</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -4485,9 +4499,9 @@
       <c r="K101" t="s">
         <v>43</v>
       </c>
-      <c r="L101" s="2" t="e">
+      <c r="L101" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41694.145076801855</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -4524,9 +4538,9 @@
       <c r="K102" t="s">
         <v>16</v>
       </c>
-      <c r="L102" s="2" t="e">
+      <c r="L102" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42309.26621149393</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -4563,9 +4577,9 @@
       <c r="K103" t="s">
         <v>19</v>
       </c>
-      <c r="L103" s="2" t="e">
+      <c r="L103" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42253.211355448897</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -4602,9 +4616,9 @@
       <c r="K104" t="s">
         <v>16</v>
       </c>
-      <c r="L104" s="2" t="e">
+      <c r="L104" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40381.625240172776</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -4641,9 +4655,9 @@
       <c r="K105" t="s">
         <v>22</v>
       </c>
-      <c r="L105" s="2" t="e">
+      <c r="L105" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40760.282169729835</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -4680,9 +4694,9 @@
       <c r="K106" t="s">
         <v>14</v>
       </c>
-      <c r="L106" s="2" t="e">
+      <c r="L106" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42257.163603927307</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -4719,9 +4733,9 @@
       <c r="K107" t="s">
         <v>31</v>
       </c>
-      <c r="L107" s="2" t="e">
+      <c r="L107" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41469.452189552176</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
@@ -4758,9 +4772,9 @@
       <c r="K108" t="s">
         <v>39</v>
       </c>
-      <c r="L108" s="2" t="e">
+      <c r="L108" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40899.820293651828</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -4797,9 +4811,9 @@
       <c r="K109" t="s">
         <v>31</v>
       </c>
-      <c r="L109" s="2" t="e">
+      <c r="L109" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41523.003177405139</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -4836,9 +4850,9 @@
       <c r="K110" t="s">
         <v>18</v>
       </c>
-      <c r="L110" s="2" t="e">
+      <c r="L110" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41115.908364789328</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -4875,9 +4889,9 @@
       <c r="K111" t="s">
         <v>39</v>
       </c>
-      <c r="L111" s="2" t="e">
+      <c r="L111" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41386.683230845316</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -4914,9 +4928,9 @@
       <c r="K112" t="s">
         <v>43</v>
       </c>
-      <c r="L112" s="2" t="e">
+      <c r="L112" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41345.899351627042</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -4953,9 +4967,9 @@
       <c r="K113" t="s">
         <v>31</v>
       </c>
-      <c r="L113" s="2" t="e">
+      <c r="L113" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41121.096592563546</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
@@ -4992,9 +5006,9 @@
       <c r="K114" t="s">
         <v>16</v>
       </c>
-      <c r="L114" s="2" t="e">
+      <c r="L114" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40340.393509114576</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -5031,9 +5045,9 @@
       <c r="K115" t="s">
         <v>39</v>
       </c>
-      <c r="L115" s="2" t="e">
+      <c r="L115" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41179.950423703573</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
@@ -5070,9 +5084,9 @@
       <c r="K116" t="s">
         <v>19</v>
       </c>
-      <c r="L116" s="2" t="e">
+      <c r="L116" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41764.813546063422</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
@@ -5109,9 +5123,9 @@
       <c r="K117" t="s">
         <v>43</v>
       </c>
-      <c r="L117" s="2" t="e">
+      <c r="L117" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41611.864531070452</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -5148,9 +5162,9 @@
       <c r="K118" t="s">
         <v>22</v>
       </c>
-      <c r="L118" s="2" t="e">
+      <c r="L118" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42321.635206237719</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
@@ -5187,9 +5201,9 @@
       <c r="K119" t="s">
         <v>31</v>
       </c>
-      <c r="L119" s="2" t="e">
+      <c r="L119" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40660.290907494134</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -5226,9 +5240,9 @@
       <c r="K120" t="s">
         <v>39</v>
       </c>
-      <c r="L120" s="2" t="e">
+      <c r="L120" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41658.246273645171</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
@@ -5265,9 +5279,9 @@
       <c r="K121" t="s">
         <v>31</v>
       </c>
-      <c r="L121" s="2" t="e">
+      <c r="L121" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40456.165358534548</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -5304,9 +5318,9 @@
       <c r="K122" t="s">
         <v>19</v>
       </c>
-      <c r="L122" s="2" t="e">
+      <c r="L122" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40952.837848534502</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -5343,9 +5357,9 @@
       <c r="K123" t="s">
         <v>19</v>
       </c>
-      <c r="L123" s="2" t="e">
+      <c r="L123" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41572.709654034741</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -5382,9 +5396,9 @@
       <c r="K124" t="s">
         <v>19</v>
       </c>
-      <c r="L124" s="2" t="e">
+      <c r="L124" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41690.459247928964</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -5421,9 +5435,9 @@
       <c r="K125" t="s">
         <v>43</v>
       </c>
-      <c r="L125" s="2" t="e">
+      <c r="L125" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42039.845728975954</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -5460,9 +5474,9 @@
       <c r="K126" t="s">
         <v>36</v>
       </c>
-      <c r="L126" s="2" t="e">
+      <c r="L126" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41967.843393009927</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -5499,9 +5513,9 @@
       <c r="K127" t="s">
         <v>26</v>
       </c>
-      <c r="L127" s="2" t="e">
+      <c r="L127" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42255.886980915449</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -5538,9 +5552,9 @@
       <c r="K128" t="s">
         <v>26</v>
       </c>
-      <c r="L128" s="2" t="e">
+      <c r="L128" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40334.913949870264</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
@@ -5577,9 +5591,9 @@
       <c r="K129" t="s">
         <v>36</v>
       </c>
-      <c r="L129" s="2" t="e">
+      <c r="L129" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40420.811853795094</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -5616,9 +5630,9 @@
       <c r="K130" t="s">
         <v>14</v>
       </c>
-      <c r="L130" s="2" t="e">
+      <c r="L130" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41477.649312951493</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
@@ -5655,9 +5669,9 @@
       <c r="K131" t="s">
         <v>36</v>
       </c>
-      <c r="L131" s="2" t="e">
+      <c r="L131" s="2">
         <f t="shared" ref="L131:L194" ca="1" si="2">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40843.077506128197</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -5694,9 +5708,9 @@
       <c r="K132" t="s">
         <v>14</v>
       </c>
-      <c r="L132" s="2" t="e">
+      <c r="L132" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41835.014109126794</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -5733,9 +5747,9 @@
       <c r="K133" t="s">
         <v>26</v>
       </c>
-      <c r="L133" s="2" t="e">
+      <c r="L133" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41866.470421498845</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -5772,9 +5786,9 @@
       <c r="K134" t="s">
         <v>19</v>
       </c>
-      <c r="L134" s="2" t="e">
+      <c r="L134" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41678.974493434092</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -5811,9 +5825,9 @@
       <c r="K135" t="s">
         <v>39</v>
       </c>
-      <c r="L135" s="2" t="e">
+      <c r="L135" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40905.88965475974</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -5850,9 +5864,9 @@
       <c r="K136" t="s">
         <v>19</v>
       </c>
-      <c r="L136" s="2" t="e">
+      <c r="L136" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41839.322439860051</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
@@ -5889,9 +5903,9 @@
       <c r="K137" t="s">
         <v>36</v>
       </c>
-      <c r="L137" s="2" t="e">
+      <c r="L137" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41054.098187413852</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
@@ -5928,9 +5942,9 @@
       <c r="K138" t="s">
         <v>18</v>
       </c>
-      <c r="L138" s="2" t="e">
+      <c r="L138" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41970.047535735939</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -5967,9 +5981,9 @@
       <c r="K139" t="s">
         <v>39</v>
       </c>
-      <c r="L139" s="2" t="e">
+      <c r="L139" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42082.118700156381</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -6006,9 +6020,9 @@
       <c r="K140" t="s">
         <v>19</v>
       </c>
-      <c r="L140" s="2" t="e">
+      <c r="L140" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40213.457901254784</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -6045,9 +6059,9 @@
       <c r="K141" t="s">
         <v>36</v>
       </c>
-      <c r="L141" s="2" t="e">
+      <c r="L141" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41751.042869094294</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
@@ -6084,9 +6098,9 @@
       <c r="K142" t="s">
         <v>19</v>
       </c>
-      <c r="L142" s="2" t="e">
+      <c r="L142" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40867.184706630018</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6123,9 +6137,9 @@
       <c r="K143" t="s">
         <v>31</v>
       </c>
-      <c r="L143" s="2" t="e">
+      <c r="L143" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41022.877732272427</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -6162,9 +6176,9 @@
       <c r="K144" t="s">
         <v>16</v>
       </c>
-      <c r="L144" s="2" t="e">
+      <c r="L144" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41111.516212581613</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -6201,9 +6215,9 @@
       <c r="K145" t="s">
         <v>19</v>
       </c>
-      <c r="L145" s="2" t="e">
+      <c r="L145" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40403.46241870302</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -6240,9 +6254,9 @@
       <c r="K146" t="s">
         <v>31</v>
       </c>
-      <c r="L146" s="2" t="e">
+      <c r="L146" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40747.527020974609</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -6279,9 +6293,9 @@
       <c r="K147" t="s">
         <v>18</v>
       </c>
-      <c r="L147" s="2" t="e">
+      <c r="L147" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41446.605933899773</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -6318,9 +6332,9 @@
       <c r="K148" t="s">
         <v>14</v>
       </c>
-      <c r="L148" s="2" t="e">
+      <c r="L148" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40770.88104531321</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -6357,9 +6371,9 @@
       <c r="K149" t="s">
         <v>18</v>
       </c>
-      <c r="L149" s="2" t="e">
+      <c r="L149" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41090.182866740404</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -6396,9 +6410,9 @@
       <c r="K150" t="s">
         <v>16</v>
       </c>
-      <c r="L150" s="2" t="e">
+      <c r="L150" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42247.284112999936</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -6435,9 +6449,9 @@
       <c r="K151" t="s">
         <v>16</v>
       </c>
-      <c r="L151" s="2" t="e">
+      <c r="L151" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40648.450710280245</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -6474,9 +6488,9 @@
       <c r="K152" t="s">
         <v>16</v>
       </c>
-      <c r="L152" s="2" t="e">
+      <c r="L152" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42036.613840630554</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -6513,9 +6527,9 @@
       <c r="K153" t="s">
         <v>19</v>
       </c>
-      <c r="L153" s="2" t="e">
+      <c r="L153" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40904.024787068811</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -6552,9 +6566,9 @@
       <c r="K154" t="s">
         <v>26</v>
       </c>
-      <c r="L154" s="2" t="e">
+      <c r="L154" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40601.35746052894</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
@@ -6591,9 +6605,9 @@
       <c r="K155" t="s">
         <v>26</v>
       </c>
-      <c r="L155" s="2" t="e">
+      <c r="L155" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40798.236626044622</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
@@ -6630,9 +6644,9 @@
       <c r="K156" t="s">
         <v>18</v>
       </c>
-      <c r="L156" s="2" t="e">
+      <c r="L156" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40593.857158301056</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
@@ -6669,9 +6683,9 @@
       <c r="K157" t="s">
         <v>19</v>
       </c>
-      <c r="L157" s="2" t="e">
+      <c r="L157" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41459.460969953601</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
@@ -6708,9 +6722,9 @@
       <c r="K158" t="s">
         <v>36</v>
       </c>
-      <c r="L158" s="2" t="e">
+      <c r="L158" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40323.561474621813</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -6747,9 +6761,9 @@
       <c r="K159" t="s">
         <v>39</v>
       </c>
-      <c r="L159" s="2" t="e">
+      <c r="L159" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42018.503544666033</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
@@ -6786,9 +6800,9 @@
       <c r="K160" t="s">
         <v>26</v>
       </c>
-      <c r="L160" s="2" t="e">
+      <c r="L160" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40709.278994302629</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -6825,9 +6839,9 @@
       <c r="K161" t="s">
         <v>14</v>
       </c>
-      <c r="L161" s="2" t="e">
+      <c r="L161" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40527.74126929653</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -6864,9 +6878,9 @@
       <c r="K162" t="s">
         <v>36</v>
       </c>
-      <c r="L162" s="2" t="e">
+      <c r="L162" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40500.066195666041</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
@@ -6903,9 +6917,9 @@
       <c r="K163" t="s">
         <v>36</v>
       </c>
-      <c r="L163" s="2" t="e">
+      <c r="L163" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41797.351172048671</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -6942,9 +6956,9 @@
       <c r="K164" t="s">
         <v>14</v>
       </c>
-      <c r="L164" s="2" t="e">
+      <c r="L164" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40333.10575026679</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
@@ -6981,9 +6995,9 @@
       <c r="K165" t="s">
         <v>18</v>
       </c>
-      <c r="L165" s="2" t="e">
+      <c r="L165" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40987.290429184381</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7020,9 +7034,9 @@
       <c r="K166" t="s">
         <v>31</v>
       </c>
-      <c r="L166" s="2" t="e">
+      <c r="L166" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41585.867778808941</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -7059,9 +7073,9 @@
       <c r="K167" t="s">
         <v>31</v>
       </c>
-      <c r="L167" s="2" t="e">
+      <c r="L167" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42167.781663327485</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
@@ -7098,9 +7112,9 @@
       <c r="K168" t="s">
         <v>36</v>
       </c>
-      <c r="L168" s="2" t="e">
+      <c r="L168" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41042.640994279616</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -7137,9 +7151,9 @@
       <c r="K169" t="s">
         <v>16</v>
       </c>
-      <c r="L169" s="2" t="e">
+      <c r="L169" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41212.932194411413</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -7176,9 +7190,9 @@
       <c r="K170" t="s">
         <v>43</v>
       </c>
-      <c r="L170" s="2" t="e">
+      <c r="L170" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41527.62707168897</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -7215,9 +7229,9 @@
       <c r="K171" t="s">
         <v>31</v>
       </c>
-      <c r="L171" s="2" t="e">
+      <c r="L171" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42317.893910354425</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7254,9 +7268,9 @@
       <c r="K172" t="s">
         <v>39</v>
       </c>
-      <c r="L172" s="2" t="e">
+      <c r="L172" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41565.164665870165</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -7293,9 +7307,9 @@
       <c r="K173" t="s">
         <v>22</v>
       </c>
-      <c r="L173" s="2" t="e">
+      <c r="L173" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41942.740355532136</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7332,9 +7346,9 @@
       <c r="K174" t="s">
         <v>19</v>
       </c>
-      <c r="L174" s="2" t="e">
+      <c r="L174" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40596.46371640265</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
@@ -7371,9 +7385,9 @@
       <c r="K175" t="s">
         <v>18</v>
       </c>
-      <c r="L175" s="2" t="e">
+      <c r="L175" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42212.714758083916</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -7410,9 +7424,9 @@
       <c r="K176" t="s">
         <v>31</v>
       </c>
-      <c r="L176" s="2" t="e">
+      <c r="L176" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41009.436623874892</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -7449,9 +7463,9 @@
       <c r="K177" t="s">
         <v>31</v>
       </c>
-      <c r="L177" s="2" t="e">
+      <c r="L177" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40901.568832897268</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
@@ -7488,9 +7502,9 @@
       <c r="K178" t="s">
         <v>14</v>
       </c>
-      <c r="L178" s="2" t="e">
+      <c r="L178" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41253.208046945561</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -7527,9 +7541,9 @@
       <c r="K179" t="s">
         <v>36</v>
       </c>
-      <c r="L179" s="2" t="e">
+      <c r="L179" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41945.283548178697</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -7566,9 +7580,9 @@
       <c r="K180" t="s">
         <v>18</v>
       </c>
-      <c r="L180" s="2" t="e">
+      <c r="L180" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41092.327910768894</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -7605,9 +7619,9 @@
       <c r="K181" t="s">
         <v>18</v>
       </c>
-      <c r="L181" s="2" t="e">
+      <c r="L181" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40649.904225685663</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -7644,9 +7658,9 @@
       <c r="K182" t="s">
         <v>39</v>
       </c>
-      <c r="L182" s="2" t="e">
+      <c r="L182" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40862.640062566177</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -7683,9 +7697,9 @@
       <c r="K183" t="s">
         <v>18</v>
       </c>
-      <c r="L183" s="2" t="e">
+      <c r="L183" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41829.944258956843</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
@@ -7722,9 +7736,9 @@
       <c r="K184" t="s">
         <v>14</v>
       </c>
-      <c r="L184" s="2" t="e">
+      <c r="L184" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40816.387116592254</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
@@ -7761,9 +7775,9 @@
       <c r="K185" t="s">
         <v>22</v>
       </c>
-      <c r="L185" s="2" t="e">
+      <c r="L185" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41951.732917205554</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
@@ -7800,9 +7814,9 @@
       <c r="K186" t="s">
         <v>39</v>
       </c>
-      <c r="L186" s="2" t="e">
+      <c r="L186" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42174.779355639221</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -7839,9 +7853,9 @@
       <c r="K187" t="s">
         <v>18</v>
       </c>
-      <c r="L187" s="2" t="e">
+      <c r="L187" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41446.219673527739</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -7878,9 +7892,9 @@
       <c r="K188" t="s">
         <v>39</v>
       </c>
-      <c r="L188" s="2" t="e">
+      <c r="L188" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41458.418091415449</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
@@ -7917,9 +7931,9 @@
       <c r="K189" t="s">
         <v>22</v>
       </c>
-      <c r="L189" s="2" t="e">
+      <c r="L189" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41626.191753850093</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
@@ -7956,9 +7970,9 @@
       <c r="K190" t="s">
         <v>39</v>
       </c>
-      <c r="L190" s="2" t="e">
+      <c r="L190" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40974.86368663529</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -7995,9 +8009,9 @@
       <c r="K191" t="s">
         <v>18</v>
       </c>
-      <c r="L191" s="2" t="e">
+      <c r="L191" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41429.660816253847</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
@@ -8034,9 +8048,9 @@
       <c r="K192" t="s">
         <v>43</v>
       </c>
-      <c r="L192" s="2" t="e">
+      <c r="L192" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40279.29165426673</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
@@ -8073,9 +8087,9 @@
       <c r="K193" t="s">
         <v>39</v>
       </c>
-      <c r="L193" s="2" t="e">
+      <c r="L193" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41478.967729637079</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -8112,9 +8126,9 @@
       <c r="K194" t="s">
         <v>39</v>
       </c>
-      <c r="L194" s="2" t="e">
+      <c r="L194" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41648.133708471069</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
@@ -8151,9 +8165,9 @@
       <c r="K195" t="s">
         <v>39</v>
       </c>
-      <c r="L195" s="2" t="e">
+      <c r="L195" s="2">
         <f t="shared" ref="L195:L258" ca="1" si="3">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41064.843859248838</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -8190,9 +8204,9 @@
       <c r="K196" t="s">
         <v>18</v>
       </c>
-      <c r="L196" s="2" t="e">
+      <c r="L196" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41899.215427062743</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
@@ -8229,9 +8243,9 @@
       <c r="K197" t="s">
         <v>31</v>
       </c>
-      <c r="L197" s="2" t="e">
+      <c r="L197" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41316.184870428813</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -8268,9 +8282,9 @@
       <c r="K198" t="s">
         <v>39</v>
       </c>
-      <c r="L198" s="2" t="e">
+      <c r="L198" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40744.973116972054</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -8307,9 +8321,9 @@
       <c r="K199" t="s">
         <v>31</v>
       </c>
-      <c r="L199" s="2" t="e">
+      <c r="L199" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41156.051207788609</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -8346,9 +8360,9 @@
       <c r="K200" t="s">
         <v>16</v>
       </c>
-      <c r="L200" s="2" t="e">
+      <c r="L200" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41488.031498943761</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -8385,9 +8399,9 @@
       <c r="K201" t="s">
         <v>14</v>
       </c>
-      <c r="L201" s="2" t="e">
+      <c r="L201" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40582.729285697249</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
@@ -8424,9 +8438,9 @@
       <c r="K202" t="s">
         <v>14</v>
       </c>
-      <c r="L202" s="2" t="e">
+      <c r="L202" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40349.272578645898</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
@@ -8463,9 +8477,9 @@
       <c r="K203" t="s">
         <v>22</v>
       </c>
-      <c r="L203" s="2" t="e">
+      <c r="L203" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41610.689316073571</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
@@ -8502,9 +8516,9 @@
       <c r="K204" t="s">
         <v>43</v>
       </c>
-      <c r="L204" s="2" t="e">
+      <c r="L204" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40860.360444905942</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
@@ -8541,9 +8555,9 @@
       <c r="K205" t="s">
         <v>22</v>
       </c>
-      <c r="L205" s="2" t="e">
+      <c r="L205" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42201.885315661944</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -8580,9 +8594,9 @@
       <c r="K206" t="s">
         <v>14</v>
       </c>
-      <c r="L206" s="2" t="e">
+      <c r="L206" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40669.618725895605</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -8619,9 +8633,9 @@
       <c r="K207" t="s">
         <v>22</v>
       </c>
-      <c r="L207" s="2" t="e">
+      <c r="L207" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41221.797115625064</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
@@ -8658,9 +8672,9 @@
       <c r="K208" t="s">
         <v>19</v>
       </c>
-      <c r="L208" s="2" t="e">
+      <c r="L208" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42204.261918415963</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
@@ -8697,9 +8711,9 @@
       <c r="K209" t="s">
         <v>39</v>
       </c>
-      <c r="L209" s="2" t="e">
+      <c r="L209" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41213.378695559382</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
@@ -8736,9 +8750,9 @@
       <c r="K210" t="s">
         <v>43</v>
       </c>
-      <c r="L210" s="2" t="e">
+      <c r="L210" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40557.606307866336</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
@@ -8775,9 +8789,9 @@
       <c r="K211" t="s">
         <v>14</v>
       </c>
-      <c r="L211" s="2" t="e">
+      <c r="L211" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40745.553946792264</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -8814,9 +8828,9 @@
       <c r="K212" t="s">
         <v>36</v>
       </c>
-      <c r="L212" s="2" t="e">
+      <c r="L212" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41503.53864067512</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
@@ -8853,9 +8867,9 @@
       <c r="K213" t="s">
         <v>14</v>
       </c>
-      <c r="L213" s="2" t="e">
+      <c r="L213" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41804.591971121452</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
@@ -8892,9 +8906,9 @@
       <c r="K214" t="s">
         <v>39</v>
       </c>
-      <c r="L214" s="2" t="e">
+      <c r="L214" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40894.726497035183</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
@@ -8931,9 +8945,9 @@
       <c r="K215" t="s">
         <v>39</v>
       </c>
-      <c r="L215" s="2" t="e">
+      <c r="L215" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41652.434131416485</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -8970,9 +8984,9 @@
       <c r="K216" t="s">
         <v>19</v>
       </c>
-      <c r="L216" s="2" t="e">
+      <c r="L216" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41090.4510520802</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
@@ -9009,9 +9023,9 @@
       <c r="K217" t="s">
         <v>31</v>
       </c>
-      <c r="L217" s="2" t="e">
+      <c r="L217" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41779.729944746432</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9048,9 +9062,9 @@
       <c r="K218" t="s">
         <v>14</v>
       </c>
-      <c r="L218" s="2" t="e">
+      <c r="L218" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40771.00255168882</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
@@ -9087,9 +9101,9 @@
       <c r="K219" t="s">
         <v>31</v>
       </c>
-      <c r="L219" s="2" t="e">
+      <c r="L219" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40209.883790750268</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
@@ -9126,9 +9140,9 @@
       <c r="K220" t="s">
         <v>43</v>
       </c>
-      <c r="L220" s="2" t="e">
+      <c r="L220" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41885.629018897998</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
@@ -9165,9 +9179,9 @@
       <c r="K221" t="s">
         <v>36</v>
       </c>
-      <c r="L221" s="2" t="e">
+      <c r="L221" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41250.41304351388</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
@@ -9204,9 +9218,9 @@
       <c r="K222" t="s">
         <v>43</v>
       </c>
-      <c r="L222" s="2" t="e">
+      <c r="L222" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42087.006551210128</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
@@ -9243,9 +9257,9 @@
       <c r="K223" t="s">
         <v>19</v>
       </c>
-      <c r="L223" s="2" t="e">
+      <c r="L223" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41788.648957563564</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
@@ -9282,9 +9296,9 @@
       <c r="K224" t="s">
         <v>31</v>
       </c>
-      <c r="L224" s="2" t="e">
+      <c r="L224" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41407.213981657354</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
@@ -9321,9 +9335,9 @@
       <c r="K225" t="s">
         <v>43</v>
       </c>
-      <c r="L225" s="2" t="e">
+      <c r="L225" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40319.939425592776</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
@@ -9360,9 +9374,9 @@
       <c r="K226" t="s">
         <v>22</v>
       </c>
-      <c r="L226" s="2" t="e">
+      <c r="L226" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40805.001654492531</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -9399,9 +9413,9 @@
       <c r="K227" t="s">
         <v>14</v>
       </c>
-      <c r="L227" s="2" t="e">
+      <c r="L227" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42255.482786510547</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
@@ -9438,9 +9452,9 @@
       <c r="K228" t="s">
         <v>18</v>
       </c>
-      <c r="L228" s="2" t="e">
+      <c r="L228" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42329.638828084469</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
@@ -9477,9 +9491,9 @@
       <c r="K229" t="s">
         <v>22</v>
       </c>
-      <c r="L229" s="2" t="e">
+      <c r="L229" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41899.11622453724</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
@@ -9516,9 +9530,9 @@
       <c r="K230" t="s">
         <v>31</v>
       </c>
-      <c r="L230" s="2" t="e">
+      <c r="L230" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42049.061383830769</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
@@ -9555,9 +9569,9 @@
       <c r="K231" t="s">
         <v>14</v>
       </c>
-      <c r="L231" s="2" t="e">
+      <c r="L231" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41250.141167845206</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
@@ -9594,9 +9608,9 @@
       <c r="K232" t="s">
         <v>43</v>
       </c>
-      <c r="L232" s="2" t="e">
+      <c r="L232" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41699.259176861277</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
@@ -9633,9 +9647,9 @@
       <c r="K233" t="s">
         <v>31</v>
       </c>
-      <c r="L233" s="2" t="e">
+      <c r="L233" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40362.693164218108</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
@@ -9672,9 +9686,9 @@
       <c r="K234" t="s">
         <v>16</v>
       </c>
-      <c r="L234" s="2" t="e">
+      <c r="L234" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41656.562907439256</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
@@ -9711,9 +9725,9 @@
       <c r="K235" t="s">
         <v>31</v>
       </c>
-      <c r="L235" s="2" t="e">
+      <c r="L235" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40676.532643401239</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
@@ -9750,9 +9764,9 @@
       <c r="K236" t="s">
         <v>14</v>
       </c>
-      <c r="L236" s="2" t="e">
+      <c r="L236" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41535.615726512682</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
@@ -9789,9 +9803,9 @@
       <c r="K237" t="s">
         <v>22</v>
       </c>
-      <c r="L237" s="2" t="e">
+      <c r="L237" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41619.125718933305</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
@@ -9828,9 +9842,9 @@
       <c r="K238" t="s">
         <v>39</v>
       </c>
-      <c r="L238" s="2" t="e">
+      <c r="L238" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40764.571710055556</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
@@ -9867,9 +9881,9 @@
       <c r="K239" t="s">
         <v>22</v>
       </c>
-      <c r="L239" s="2" t="e">
+      <c r="L239" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40700.729978850453</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
@@ -9906,9 +9920,9 @@
       <c r="K240" t="s">
         <v>26</v>
       </c>
-      <c r="L240" s="2" t="e">
+      <c r="L240" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42326.004357273952</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -9945,9 +9959,9 @@
       <c r="K241" t="s">
         <v>18</v>
       </c>
-      <c r="L241" s="2" t="e">
+      <c r="L241" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42325.903720109047</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
@@ -9984,9 +9998,9 @@
       <c r="K242" t="s">
         <v>22</v>
       </c>
-      <c r="L242" s="2" t="e">
+      <c r="L242" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41587.972980181155</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
@@ -10023,9 +10037,9 @@
       <c r="K243" t="s">
         <v>31</v>
       </c>
-      <c r="L243" s="2" t="e">
+      <c r="L243" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42274.337030499715</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
@@ -10062,9 +10076,9 @@
       <c r="K244" t="s">
         <v>36</v>
       </c>
-      <c r="L244" s="2" t="e">
+      <c r="L244" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41062.770216479636</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
@@ -10101,9 +10115,9 @@
       <c r="K245" t="s">
         <v>16</v>
       </c>
-      <c r="L245" s="2" t="e">
+      <c r="L245" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40418.037012471141</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10140,9 +10154,9 @@
       <c r="K246" t="s">
         <v>36</v>
       </c>
-      <c r="L246" s="2" t="e">
+      <c r="L246" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41997.461901061957</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
@@ -10179,9 +10193,9 @@
       <c r="K247" t="s">
         <v>16</v>
       </c>
-      <c r="L247" s="2" t="e">
+      <c r="L247" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40409.246706418235</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
@@ -10218,9 +10232,9 @@
       <c r="K248" t="s">
         <v>16</v>
       </c>
-      <c r="L248" s="2" t="e">
+      <c r="L248" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40953.652013010738</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
@@ -10257,9 +10271,9 @@
       <c r="K249" t="s">
         <v>18</v>
       </c>
-      <c r="L249" s="2" t="e">
+      <c r="L249" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41706.15850805425</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -10296,9 +10310,9 @@
       <c r="K250" t="s">
         <v>26</v>
       </c>
-      <c r="L250" s="2" t="e">
+      <c r="L250" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40378.243623921277</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
@@ -10335,9 +10349,9 @@
       <c r="K251" t="s">
         <v>43</v>
       </c>
-      <c r="L251" s="2" t="e">
+      <c r="L251" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40217.168776641214</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
@@ -10374,9 +10388,9 @@
       <c r="K252" t="s">
         <v>26</v>
       </c>
-      <c r="L252" s="2" t="e">
+      <c r="L252" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41260.156703618646</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
@@ -10413,9 +10427,9 @@
       <c r="K253" t="s">
         <v>31</v>
       </c>
-      <c r="L253" s="2" t="e">
+      <c r="L253" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41032.410155751451</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
@@ -10452,9 +10466,9 @@
       <c r="K254" t="s">
         <v>39</v>
       </c>
-      <c r="L254" s="2" t="e">
+      <c r="L254" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40609.280103336299</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
@@ -10491,9 +10505,9 @@
       <c r="K255" t="s">
         <v>18</v>
       </c>
-      <c r="L255" s="2" t="e">
+      <c r="L255" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41491.019533427701</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
@@ -10530,9 +10544,9 @@
       <c r="K256" t="s">
         <v>16</v>
       </c>
-      <c r="L256" s="2" t="e">
+      <c r="L256" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40287.215624457458</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
@@ -10569,9 +10583,9 @@
       <c r="K257" t="s">
         <v>26</v>
       </c>
-      <c r="L257" s="2" t="e">
+      <c r="L257" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40818.098159069654</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
@@ -10608,9 +10622,9 @@
       <c r="K258" t="s">
         <v>31</v>
       </c>
-      <c r="L258" s="2" t="e">
+      <c r="L258" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40425.150730949419</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
@@ -10647,9 +10661,9 @@
       <c r="K259" t="s">
         <v>18</v>
       </c>
-      <c r="L259" s="2" t="e">
+      <c r="L259" s="2">
         <f t="shared" ref="L259:L322" ca="1" si="4">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41260.991608682139</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
@@ -10686,9 +10700,9 @@
       <c r="K260" t="s">
         <v>39</v>
       </c>
-      <c r="L260" s="2" t="e">
+      <c r="L260" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40238.084970256787</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
@@ -10725,9 +10739,9 @@
       <c r="K261" t="s">
         <v>18</v>
       </c>
-      <c r="L261" s="2" t="e">
+      <c r="L261" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41255.147653322936</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
@@ -10764,9 +10778,9 @@
       <c r="K262" t="s">
         <v>18</v>
       </c>
-      <c r="L262" s="2" t="e">
+      <c r="L262" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41911.216462221739</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
@@ -10803,9 +10817,9 @@
       <c r="K263" t="s">
         <v>16</v>
       </c>
-      <c r="L263" s="2" t="e">
+      <c r="L263" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41465.550202408354</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
@@ -10842,9 +10856,9 @@
       <c r="K264" t="s">
         <v>36</v>
       </c>
-      <c r="L264" s="2" t="e">
+      <c r="L264" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42276.000966416163</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
@@ -10881,9 +10895,9 @@
       <c r="K265" t="s">
         <v>26</v>
       </c>
-      <c r="L265" s="2" t="e">
+      <c r="L265" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41973.185726414398</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
@@ -10920,9 +10934,9 @@
       <c r="K266" t="s">
         <v>36</v>
       </c>
-      <c r="L266" s="2" t="e">
+      <c r="L266" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42221.458549162904</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
@@ -10959,9 +10973,9 @@
       <c r="K267" t="s">
         <v>19</v>
       </c>
-      <c r="L267" s="2" t="e">
+      <c r="L267" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40681.713084883544</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
@@ -10998,9 +11012,9 @@
       <c r="K268" t="s">
         <v>14</v>
       </c>
-      <c r="L268" s="2" t="e">
+      <c r="L268" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41808.171813283596</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
@@ -11037,9 +11051,9 @@
       <c r="K269" t="s">
         <v>19</v>
       </c>
-      <c r="L269" s="2" t="e">
+      <c r="L269" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42317.423847980455</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
@@ -11076,9 +11090,9 @@
       <c r="K270" t="s">
         <v>22</v>
       </c>
-      <c r="L270" s="2" t="e">
+      <c r="L270" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40557.25900555362</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
@@ -11115,9 +11129,9 @@
       <c r="K271" t="s">
         <v>19</v>
       </c>
-      <c r="L271" s="2" t="e">
+      <c r="L271" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40613.219345154888</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -11154,9 +11168,9 @@
       <c r="K272" t="s">
         <v>39</v>
       </c>
-      <c r="L272" s="2" t="e">
+      <c r="L272" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40925.598204597823</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
@@ -11193,9 +11207,9 @@
       <c r="K273" t="s">
         <v>22</v>
       </c>
-      <c r="L273" s="2" t="e">
+      <c r="L273" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42173.642003323999</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
@@ -11232,9 +11246,9 @@
       <c r="K274" t="s">
         <v>18</v>
       </c>
-      <c r="L274" s="2" t="e">
+      <c r="L274" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41812.826460021177</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
@@ -11271,9 +11285,9 @@
       <c r="K275" t="s">
         <v>31</v>
       </c>
-      <c r="L275" s="2" t="e">
+      <c r="L275" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41938.501725225724</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
@@ -11310,9 +11324,9 @@
       <c r="K276" t="s">
         <v>19</v>
       </c>
-      <c r="L276" s="2" t="e">
+      <c r="L276" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40855.279564739198</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
@@ -11349,9 +11363,9 @@
       <c r="K277" t="s">
         <v>18</v>
       </c>
-      <c r="L277" s="2" t="e">
+      <c r="L277" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41698.022182787907</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
@@ -11388,9 +11402,9 @@
       <c r="K278" t="s">
         <v>18</v>
       </c>
-      <c r="L278" s="2" t="e">
+      <c r="L278" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41449.723230697979</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
@@ -11427,9 +11441,9 @@
       <c r="K279" t="s">
         <v>31</v>
       </c>
-      <c r="L279" s="2" t="e">
+      <c r="L279" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41534.496923008286</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
@@ -11466,9 +11480,9 @@
       <c r="K280" t="s">
         <v>39</v>
       </c>
-      <c r="L280" s="2" t="e">
+      <c r="L280" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42304.164781627798</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
@@ -11505,9 +11519,9 @@
       <c r="K281" t="s">
         <v>31</v>
       </c>
-      <c r="L281" s="2" t="e">
+      <c r="L281" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40251.468991141875</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
@@ -11544,9 +11558,9 @@
       <c r="K282" t="s">
         <v>18</v>
       </c>
-      <c r="L282" s="2" t="e">
+      <c r="L282" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41051.633175323346</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
@@ -11583,9 +11597,9 @@
       <c r="K283" t="s">
         <v>22</v>
       </c>
-      <c r="L283" s="2" t="e">
+      <c r="L283" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40363.228740154562</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
@@ -11622,9 +11636,9 @@
       <c r="K284" t="s">
         <v>36</v>
       </c>
-      <c r="L284" s="2" t="e">
+      <c r="L284" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42011.157381773366</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
@@ -11661,9 +11675,9 @@
       <c r="K285" t="s">
         <v>36</v>
       </c>
-      <c r="L285" s="2" t="e">
+      <c r="L285" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41847.684385505876</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -11700,9 +11714,9 @@
       <c r="K286" t="s">
         <v>22</v>
       </c>
-      <c r="L286" s="2" t="e">
+      <c r="L286" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41269.932011759876</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -11739,9 +11753,9 @@
       <c r="K287" t="s">
         <v>39</v>
       </c>
-      <c r="L287" s="2" t="e">
+      <c r="L287" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41776.270388223282</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
@@ -11778,9 +11792,9 @@
       <c r="K288" t="s">
         <v>36</v>
       </c>
-      <c r="L288" s="2" t="e">
+      <c r="L288" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40397.873343813531</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
@@ -11817,9 +11831,9 @@
       <c r="K289" t="s">
         <v>19</v>
       </c>
-      <c r="L289" s="2" t="e">
+      <c r="L289" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40976.701068279668</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
@@ -11856,9 +11870,9 @@
       <c r="K290" t="s">
         <v>16</v>
       </c>
-      <c r="L290" s="2" t="e">
+      <c r="L290" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41079.636403418008</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
@@ -11895,9 +11909,9 @@
       <c r="K291" t="s">
         <v>36</v>
       </c>
-      <c r="L291" s="2" t="e">
+      <c r="L291" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41951.365506895418</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
@@ -11934,9 +11948,9 @@
       <c r="K292" t="s">
         <v>22</v>
       </c>
-      <c r="L292" s="2" t="e">
+      <c r="L292" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41161.709912909071</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
@@ -11973,9 +11987,9 @@
       <c r="K293" t="s">
         <v>36</v>
       </c>
-      <c r="L293" s="2" t="e">
+      <c r="L293" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40975.41788380043</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
@@ -12012,9 +12026,9 @@
       <c r="K294" t="s">
         <v>26</v>
       </c>
-      <c r="L294" s="2" t="e">
+      <c r="L294" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40377.815476272917</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12051,9 +12065,9 @@
       <c r="K295" t="s">
         <v>14</v>
       </c>
-      <c r="L295" s="2" t="e">
+      <c r="L295" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42236.836916565422</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
@@ -12090,9 +12104,9 @@
       <c r="K296" t="s">
         <v>26</v>
       </c>
-      <c r="L296" s="2" t="e">
+      <c r="L296" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42376.319286358746</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
@@ -12129,9 +12143,9 @@
       <c r="K297" t="s">
         <v>19</v>
       </c>
-      <c r="L297" s="2" t="e">
+      <c r="L297" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41157.640391730034</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
@@ -12168,9 +12182,9 @@
       <c r="K298" t="s">
         <v>43</v>
       </c>
-      <c r="L298" s="2" t="e">
+      <c r="L298" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40752.5278620471</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
@@ -12207,9 +12221,9 @@
       <c r="K299" t="s">
         <v>19</v>
       </c>
-      <c r="L299" s="2" t="e">
+      <c r="L299" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41229.893367544857</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
@@ -12246,9 +12260,9 @@
       <c r="K300" t="s">
         <v>18</v>
       </c>
-      <c r="L300" s="2" t="e">
+      <c r="L300" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41865.120197796619</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -12285,9 +12299,9 @@
       <c r="K301" t="s">
         <v>36</v>
       </c>
-      <c r="L301" s="2" t="e">
+      <c r="L301" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40956.074045330752</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
@@ -12324,9 +12338,9 @@
       <c r="K302" t="s">
         <v>14</v>
       </c>
-      <c r="L302" s="2" t="e">
+      <c r="L302" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42150.871329852642</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
@@ -12363,9 +12377,9 @@
       <c r="K303" t="s">
         <v>22</v>
       </c>
-      <c r="L303" s="2" t="e">
+      <c r="L303" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42026.791634947622</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
@@ -12402,9 +12416,9 @@
       <c r="K304" t="s">
         <v>19</v>
       </c>
-      <c r="L304" s="2" t="e">
+      <c r="L304" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41863.942704433146</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
@@ -12441,9 +12455,9 @@
       <c r="K305" t="s">
         <v>16</v>
       </c>
-      <c r="L305" s="2" t="e">
+      <c r="L305" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40991.190131695141</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
@@ -12480,9 +12494,9 @@
       <c r="K306" t="s">
         <v>43</v>
       </c>
-      <c r="L306" s="2" t="e">
+      <c r="L306" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41190.850050521251</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
@@ -12519,9 +12533,9 @@
       <c r="K307" t="s">
         <v>16</v>
       </c>
-      <c r="L307" s="2" t="e">
+      <c r="L307" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40361.140059721511</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
@@ -12558,9 +12572,9 @@
       <c r="K308" t="s">
         <v>14</v>
       </c>
-      <c r="L308" s="2" t="e">
+      <c r="L308" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41799.172682087279</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
@@ -12597,9 +12611,9 @@
       <c r="K309" t="s">
         <v>18</v>
       </c>
-      <c r="L309" s="2" t="e">
+      <c r="L309" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40561.328761929144</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
@@ -12636,9 +12650,9 @@
       <c r="K310" t="s">
         <v>18</v>
       </c>
-      <c r="L310" s="2" t="e">
+      <c r="L310" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41239.972125087799</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
@@ -12675,9 +12689,9 @@
       <c r="K311" t="s">
         <v>14</v>
       </c>
-      <c r="L311" s="2" t="e">
+      <c r="L311" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41371.757411305873</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
@@ -12714,9 +12728,9 @@
       <c r="K312" t="s">
         <v>22</v>
       </c>
-      <c r="L312" s="2" t="e">
+      <c r="L312" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40497.982938978574</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
@@ -12753,9 +12767,9 @@
       <c r="K313" t="s">
         <v>36</v>
       </c>
-      <c r="L313" s="2" t="e">
+      <c r="L313" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41540.007729230871</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
@@ -12792,9 +12806,9 @@
       <c r="K314" t="s">
         <v>36</v>
       </c>
-      <c r="L314" s="2" t="e">
+      <c r="L314" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41046.663847181684</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
@@ -12831,9 +12845,9 @@
       <c r="K315" t="s">
         <v>36</v>
       </c>
-      <c r="L315" s="2" t="e">
+      <c r="L315" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42140.831877293298</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
@@ -12870,9 +12884,9 @@
       <c r="K316" t="s">
         <v>43</v>
       </c>
-      <c r="L316" s="2" t="e">
+      <c r="L316" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40231.100883616629</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
@@ -12909,9 +12923,9 @@
       <c r="K317" t="s">
         <v>22</v>
       </c>
-      <c r="L317" s="2" t="e">
+      <c r="L317" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40232.727748526515</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -12948,9 +12962,9 @@
       <c r="K318" t="s">
         <v>19</v>
       </c>
-      <c r="L318" s="2" t="e">
+      <c r="L318" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40727.578194438531</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
@@ -12987,9 +13001,9 @@
       <c r="K319" t="s">
         <v>18</v>
       </c>
-      <c r="L319" s="2" t="e">
+      <c r="L319" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41546.209155317301</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
@@ -13026,9 +13040,9 @@
       <c r="K320" t="s">
         <v>19</v>
       </c>
-      <c r="L320" s="2" t="e">
+      <c r="L320" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42134.547811074815</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
@@ -13065,9 +13079,9 @@
       <c r="K321" t="s">
         <v>26</v>
       </c>
-      <c r="L321" s="2" t="e">
+      <c r="L321" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41874.14741848658</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
@@ -13104,9 +13118,9 @@
       <c r="K322" t="s">
         <v>26</v>
       </c>
-      <c r="L322" s="2" t="e">
+      <c r="L322" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41906.32890117271</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -13143,9 +13157,9 @@
       <c r="K323" t="s">
         <v>43</v>
       </c>
-      <c r="L323" s="2" t="e">
+      <c r="L323" s="2">
         <f t="shared" ref="L323:L386" ca="1" si="5">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40279.718286608069</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
@@ -13182,9 +13196,9 @@
       <c r="K324" t="s">
         <v>39</v>
       </c>
-      <c r="L324" s="2" t="e">
+      <c r="L324" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41567.430442444718</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
@@ -13221,9 +13235,9 @@
       <c r="K325" t="s">
         <v>19</v>
       </c>
-      <c r="L325" s="2" t="e">
+      <c r="L325" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41924.105404751535</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
@@ -13260,9 +13274,9 @@
       <c r="K326" t="s">
         <v>31</v>
       </c>
-      <c r="L326" s="2" t="e">
+      <c r="L326" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41023.54390690742</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
@@ -13299,9 +13313,9 @@
       <c r="K327" t="s">
         <v>36</v>
       </c>
-      <c r="L327" s="2" t="e">
+      <c r="L327" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40830.970807881953</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
@@ -13338,9 +13352,9 @@
       <c r="K328" t="s">
         <v>26</v>
       </c>
-      <c r="L328" s="2" t="e">
+      <c r="L328" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40802.227601724946</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.3">
@@ -13377,9 +13391,9 @@
       <c r="K329" t="s">
         <v>14</v>
       </c>
-      <c r="L329" s="2" t="e">
+      <c r="L329" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40928.395550373825</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
@@ -13416,9 +13430,9 @@
       <c r="K330" t="s">
         <v>26</v>
       </c>
-      <c r="L330" s="2" t="e">
+      <c r="L330" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41242.032653750357</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
@@ -13455,9 +13469,9 @@
       <c r="K331" t="s">
         <v>18</v>
       </c>
-      <c r="L331" s="2" t="e">
+      <c r="L331" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42232.799363889419</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
@@ -13494,9 +13508,9 @@
       <c r="K332" t="s">
         <v>31</v>
       </c>
-      <c r="L332" s="2" t="e">
+      <c r="L332" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41419.969877493124</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
@@ -13533,9 +13547,9 @@
       <c r="K333" t="s">
         <v>26</v>
       </c>
-      <c r="L333" s="2" t="e">
+      <c r="L333" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40672.07830958713</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
@@ -13572,9 +13586,9 @@
       <c r="K334" t="s">
         <v>19</v>
       </c>
-      <c r="L334" s="2" t="e">
+      <c r="L334" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40885.940565640252</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
@@ -13611,9 +13625,9 @@
       <c r="K335" t="s">
         <v>16</v>
       </c>
-      <c r="L335" s="2" t="e">
+      <c r="L335" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40842.681913625529</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
@@ -13650,9 +13664,9 @@
       <c r="K336" t="s">
         <v>39</v>
       </c>
-      <c r="L336" s="2" t="e">
+      <c r="L336" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41826.245121088403</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
@@ -13689,9 +13703,9 @@
       <c r="K337" t="s">
         <v>31</v>
       </c>
-      <c r="L337" s="2" t="e">
+      <c r="L337" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41080.648966832203</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.3">
@@ -13728,9 +13742,9 @@
       <c r="K338" t="s">
         <v>19</v>
       </c>
-      <c r="L338" s="2" t="e">
+      <c r="L338" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41510.200350569001</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
@@ -13767,9 +13781,9 @@
       <c r="K339" t="s">
         <v>14</v>
       </c>
-      <c r="L339" s="2" t="e">
+      <c r="L339" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41396.15826137564</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
@@ -13806,9 +13820,9 @@
       <c r="K340" t="s">
         <v>19</v>
       </c>
-      <c r="L340" s="2" t="e">
+      <c r="L340" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40851.265211334598</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
@@ -13845,9 +13859,9 @@
       <c r="K341" t="s">
         <v>39</v>
       </c>
-      <c r="L341" s="2" t="e">
+      <c r="L341" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40300.899504098183</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
@@ -13884,9 +13898,9 @@
       <c r="K342" t="s">
         <v>18</v>
       </c>
-      <c r="L342" s="2" t="e">
+      <c r="L342" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41226.066567645932</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
@@ -13923,9 +13937,9 @@
       <c r="K343" t="s">
         <v>26</v>
       </c>
-      <c r="L343" s="2" t="e">
+      <c r="L343" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41234.435087389189</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
@@ -13962,9 +13976,9 @@
       <c r="K344" t="s">
         <v>39</v>
       </c>
-      <c r="L344" s="2" t="e">
+      <c r="L344" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41751.091149542233</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
@@ -14001,9 +14015,9 @@
       <c r="K345" t="s">
         <v>26</v>
       </c>
-      <c r="L345" s="2" t="e">
+      <c r="L345" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41342.395612697233</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
@@ -14040,9 +14054,9 @@
       <c r="K346" t="s">
         <v>14</v>
       </c>
-      <c r="L346" s="2" t="e">
+      <c r="L346" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41539.327021570251</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
@@ -14079,9 +14093,9 @@
       <c r="K347" t="s">
         <v>31</v>
       </c>
-      <c r="L347" s="2" t="e">
+      <c r="L347" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40390.408859691204</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -14118,9 +14132,9 @@
       <c r="K348" t="s">
         <v>39</v>
       </c>
-      <c r="L348" s="2" t="e">
+      <c r="L348" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41337.091235256696</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
@@ -14157,9 +14171,9 @@
       <c r="K349" t="s">
         <v>22</v>
       </c>
-      <c r="L349" s="2" t="e">
+      <c r="L349" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40416.595233209082</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
@@ -14196,9 +14210,9 @@
       <c r="K350" t="s">
         <v>18</v>
       </c>
-      <c r="L350" s="2" t="e">
+      <c r="L350" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40683.122369115081</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
@@ -14235,9 +14249,9 @@
       <c r="K351" t="s">
         <v>31</v>
       </c>
-      <c r="L351" s="2" t="e">
+      <c r="L351" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41843.432299637636</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -14274,9 +14288,9 @@
       <c r="K352" t="s">
         <v>31</v>
       </c>
-      <c r="L352" s="2" t="e">
+      <c r="L352" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42232.52255551298</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
@@ -14313,9 +14327,9 @@
       <c r="K353" t="s">
         <v>18</v>
       </c>
-      <c r="L353" s="2" t="e">
+      <c r="L353" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40749.154577234054</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
@@ -14352,9 +14366,9 @@
       <c r="K354" t="s">
         <v>43</v>
       </c>
-      <c r="L354" s="2" t="e">
+      <c r="L354" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42070.339280864551</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -14391,9 +14405,9 @@
       <c r="K355" t="s">
         <v>26</v>
       </c>
-      <c r="L355" s="2" t="e">
+      <c r="L355" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41320.612407587672</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -14430,9 +14444,9 @@
       <c r="K356" t="s">
         <v>14</v>
       </c>
-      <c r="L356" s="2" t="e">
+      <c r="L356" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41594.29924158223</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
@@ -14469,9 +14483,9 @@
       <c r="K357" t="s">
         <v>22</v>
       </c>
-      <c r="L357" s="2" t="e">
+      <c r="L357" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42376.877857618936</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -14508,9 +14522,9 @@
       <c r="K358" t="s">
         <v>31</v>
       </c>
-      <c r="L358" s="2" t="e">
+      <c r="L358" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40231.636385653743</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -14547,9 +14561,9 @@
       <c r="K359" t="s">
         <v>39</v>
       </c>
-      <c r="L359" s="2" t="e">
+      <c r="L359" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41407.609939277871</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
@@ -14586,9 +14600,9 @@
       <c r="K360" t="s">
         <v>19</v>
       </c>
-      <c r="L360" s="2" t="e">
+      <c r="L360" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41663.758524435318</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -14625,9 +14639,9 @@
       <c r="K361" t="s">
         <v>22</v>
       </c>
-      <c r="L361" s="2" t="e">
+      <c r="L361" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41092.166392993029</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.3">
@@ -14664,9 +14678,9 @@
       <c r="K362" t="s">
         <v>22</v>
       </c>
-      <c r="L362" s="2" t="e">
+      <c r="L362" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42150.58888062105</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
@@ -14703,9 +14717,9 @@
       <c r="K363" t="s">
         <v>26</v>
       </c>
-      <c r="L363" s="2" t="e">
+      <c r="L363" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41041.706468360513</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -14742,9 +14756,9 @@
       <c r="K364" t="s">
         <v>18</v>
       </c>
-      <c r="L364" s="2" t="e">
+      <c r="L364" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40313.66153930287</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
@@ -14781,9 +14795,9 @@
       <c r="K365" t="s">
         <v>39</v>
       </c>
-      <c r="L365" s="2" t="e">
+      <c r="L365" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40287.592930641615</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
@@ -14820,9 +14834,9 @@
       <c r="K366" t="s">
         <v>22</v>
       </c>
-      <c r="L366" s="2" t="e">
+      <c r="L366" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40988.251237491895</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
@@ -14859,9 +14873,9 @@
       <c r="K367" t="s">
         <v>18</v>
       </c>
-      <c r="L367" s="2" t="e">
+      <c r="L367" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41850.718350160285</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
@@ -14898,9 +14912,9 @@
       <c r="K368" t="s">
         <v>26</v>
       </c>
-      <c r="L368" s="2" t="e">
+      <c r="L368" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41654.477266425907</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
@@ -14937,9 +14951,9 @@
       <c r="K369" t="s">
         <v>39</v>
       </c>
-      <c r="L369" s="2" t="e">
+      <c r="L369" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40399.837593980214</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
@@ -14976,9 +14990,9 @@
       <c r="K370" t="s">
         <v>22</v>
       </c>
-      <c r="L370" s="2" t="e">
+      <c r="L370" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40392.938106930007</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
@@ -15015,9 +15029,9 @@
       <c r="K371" t="s">
         <v>39</v>
       </c>
-      <c r="L371" s="2" t="e">
+      <c r="L371" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40714.404234982481</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
@@ -15054,9 +15068,9 @@
       <c r="K372" t="s">
         <v>16</v>
       </c>
-      <c r="L372" s="2" t="e">
+      <c r="L372" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41616.319325517121</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
@@ -15093,9 +15107,9 @@
       <c r="K373" t="s">
         <v>16</v>
       </c>
-      <c r="L373" s="2" t="e">
+      <c r="L373" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41873.457420518906</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
@@ -15132,9 +15146,9 @@
       <c r="K374" t="s">
         <v>22</v>
       </c>
-      <c r="L374" s="2" t="e">
+      <c r="L374" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42097.676697012561</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
@@ -15171,9 +15185,9 @@
       <c r="K375" t="s">
         <v>16</v>
       </c>
-      <c r="L375" s="2" t="e">
+      <c r="L375" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40534.690790162458</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
@@ -15210,9 +15224,9 @@
       <c r="K376" t="s">
         <v>43</v>
       </c>
-      <c r="L376" s="2" t="e">
+      <c r="L376" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41558.843266715514</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
@@ -15249,9 +15263,9 @@
       <c r="K377" t="s">
         <v>31</v>
       </c>
-      <c r="L377" s="2" t="e">
+      <c r="L377" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40854.373782680021</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -15288,9 +15302,9 @@
       <c r="K378" t="s">
         <v>19</v>
       </c>
-      <c r="L378" s="2" t="e">
+      <c r="L378" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40451.299177990892</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
@@ -15327,9 +15341,9 @@
       <c r="K379" t="s">
         <v>36</v>
       </c>
-      <c r="L379" s="2" t="e">
+      <c r="L379" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40932.557784899327</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
@@ -15366,9 +15380,9 @@
       <c r="K380" t="s">
         <v>31</v>
       </c>
-      <c r="L380" s="2" t="e">
+      <c r="L380" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41943.660967266514</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
@@ -15405,9 +15419,9 @@
       <c r="K381" t="s">
         <v>26</v>
       </c>
-      <c r="L381" s="2" t="e">
+      <c r="L381" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42100.115955886482</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
@@ -15444,9 +15458,9 @@
       <c r="K382" t="s">
         <v>19</v>
       </c>
-      <c r="L382" s="2" t="e">
+      <c r="L382" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41782.344298911965</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
@@ -15483,9 +15497,9 @@
       <c r="K383" t="s">
         <v>43</v>
       </c>
-      <c r="L383" s="2" t="e">
+      <c r="L383" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41902.158169754082</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -15522,9 +15536,9 @@
       <c r="K384" t="s">
         <v>31</v>
       </c>
-      <c r="L384" s="2" t="e">
+      <c r="L384" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40721.013066266692</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
@@ -15561,9 +15575,9 @@
       <c r="K385" t="s">
         <v>39</v>
       </c>
-      <c r="L385" s="2" t="e">
+      <c r="L385" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40609.575068176018</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.3">
@@ -15600,9 +15614,9 @@
       <c r="K386" t="s">
         <v>43</v>
       </c>
-      <c r="L386" s="2" t="e">
+      <c r="L386" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41814.441766642551</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
@@ -15639,9 +15653,9 @@
       <c r="K387" t="s">
         <v>19</v>
       </c>
-      <c r="L387" s="2" t="e">
+      <c r="L387" s="2">
         <f t="shared" ref="L387:L392" ca="1" si="6">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41716.580103695997</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
@@ -15678,9 +15692,9 @@
       <c r="K388" t="s">
         <v>14</v>
       </c>
-      <c r="L388" s="2" t="e">
+      <c r="L388" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v>#VALUE!</v>
+        <v>41738.380157513777</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
@@ -15717,9 +15731,9 @@
       <c r="K389" t="s">
         <v>31</v>
       </c>
-      <c r="L389" s="2" t="e">
+      <c r="L389" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v>#VALUE!</v>
+        <v>42111.145309988235</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
@@ -15756,9 +15770,9 @@
       <c r="K390" t="s">
         <v>22</v>
       </c>
-      <c r="L390" s="2" t="e">
+      <c r="L390" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v>#VALUE!</v>
+        <v>41597.51345131483</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.3">
@@ -15795,9 +15809,9 @@
       <c r="K391" t="s">
         <v>26</v>
       </c>
-      <c r="L391" s="2" t="e">
+      <c r="L391" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v>#VALUE!</v>
+        <v>41913.248670516907</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.3">
@@ -15834,9 +15848,9 @@
       <c r="K392" t="s">
         <v>39</v>
       </c>
-      <c r="L392" s="2" t="e">
+      <c r="L392" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v>#VALUE!</v>
+        <v>41074.269157950112</v>
       </c>
     </row>
   </sheetData>
